--- a/artfynd/A 401-2023 artfynd.xlsx
+++ b/artfynd/A 401-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,322 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125979817</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78373</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Mörtsjön, 500 m S om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>504801</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6533174</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>kalhuggen våtmark</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125979306</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58507</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mörtsjön, 500 m S om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>504825</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6533191</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>kalhuggen våtmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125979595</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98251</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stora Janneberg, O om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>504764</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6532946</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>ung, dikad sumpskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 401-2023 artfynd.xlsx
+++ b/artfynd/A 401-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>125979817</v>
       </c>
       <c r="B3" t="n">
-        <v>78373</v>
+        <v>78374</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>125979306</v>
       </c>
       <c r="B4" t="n">
-        <v>58507</v>
+        <v>58508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>125979595</v>
       </c>
       <c r="B5" t="n">
-        <v>98251</v>
+        <v>98252</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 401-2023 artfynd.xlsx
+++ b/artfynd/A 401-2023 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>125979595</v>
       </c>
       <c r="B5" t="n">
-        <v>98252</v>
+        <v>98254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 401-2023 artfynd.xlsx
+++ b/artfynd/A 401-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>125979817</v>
       </c>
       <c r="B3" t="n">
-        <v>78374</v>
+        <v>78378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>125979595</v>
       </c>
       <c r="B5" t="n">
-        <v>98254</v>
+        <v>98258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 401-2023 artfynd.xlsx
+++ b/artfynd/A 401-2023 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>125979595</v>
       </c>
       <c r="B5" t="n">
-        <v>98258</v>
+        <v>98259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 401-2023 artfynd.xlsx
+++ b/artfynd/A 401-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>125979817</v>
       </c>
       <c r="B3" t="n">
-        <v>78378</v>
+        <v>78379</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>125979306</v>
       </c>
       <c r="B4" t="n">
-        <v>58508</v>
+        <v>58509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>125979595</v>
       </c>
       <c r="B5" t="n">
-        <v>98259</v>
+        <v>98261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 401-2023 artfynd.xlsx
+++ b/artfynd/A 401-2023 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>125979595</v>
       </c>
       <c r="B5" t="n">
-        <v>98261</v>
+        <v>98263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 401-2023 artfynd.xlsx
+++ b/artfynd/A 401-2023 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>125979595</v>
       </c>
       <c r="B5" t="n">
-        <v>98263</v>
+        <v>98265</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 401-2023 artfynd.xlsx
+++ b/artfynd/A 401-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>125979817</v>
       </c>
       <c r="B3" t="n">
-        <v>78379</v>
+        <v>78383</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>125979306</v>
       </c>
       <c r="B4" t="n">
-        <v>58509</v>
+        <v>58513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>125979595</v>
       </c>
       <c r="B5" t="n">
-        <v>98265</v>
+        <v>98269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 401-2023 artfynd.xlsx
+++ b/artfynd/A 401-2023 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>125979595</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
+        <v>98272</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 401-2023 artfynd.xlsx
+++ b/artfynd/A 401-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>125979817</v>
       </c>
       <c r="B3" t="n">
-        <v>78383</v>
+        <v>78386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>125979306</v>
       </c>
       <c r="B4" t="n">
-        <v>58513</v>
+        <v>58516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>125979595</v>
       </c>
       <c r="B5" t="n">
-        <v>98272</v>
+        <v>98281</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 401-2023 artfynd.xlsx
+++ b/artfynd/A 401-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118171591</v>
+        <v>125979817</v>
       </c>
       <c r="B2" t="n">
-        <v>96804</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hagaberg, 450 m V om, Nrk</t>
+          <t>Mörtsjön, 500 m S om, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504880</v>
+        <v>504801</v>
       </c>
       <c r="R2" t="n">
-        <v>6533118</v>
+        <v>6533174</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +759,17 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>skogsbilvägkant</t>
+          <t>kalhuggen våtmark</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125979817</v>
+        <v>129782196</v>
       </c>
       <c r="B3" t="n">
-        <v>78386</v>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +798,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mörtsjön, 500 m S om, Nrk</t>
+          <t>Mörtsjön, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504801</v>
+        <v>504882</v>
       </c>
       <c r="R3" t="n">
-        <v>6533174</v>
+        <v>6533259</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -863,79 +873,82 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>kalhuggen våtmark</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Jan Måreby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Jan Måreby</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Fågelinventering Vätternvatten 2024</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125979306</v>
+        <v>121370634</v>
       </c>
       <c r="B4" t="n">
-        <v>58516</v>
+        <v>56816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>detektor med heterodyn</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mörtsjön, 500 m S om, Nrk</t>
+          <t>AT4, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504825</v>
+        <v>504894</v>
       </c>
       <c r="R4" t="n">
-        <v>6533191</v>
+        <v>6533109</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,12 +972,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -975,31 +988,30 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>kalhuggen våtmark</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Adina Sennblad (AFRY)</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Adina Sennblad (AFRY), Ann Johansson, Annelie Thor</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Artkartering projekt. Hallsberg-askersund</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125979595</v>
+        <v>125979306</v>
       </c>
       <c r="B5" t="n">
-        <v>98281</v>
+        <v>58817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1019,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223597</v>
+        <v>208249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stora Janneberg, O om, Nrk</t>
+          <t>Mörtsjön, 500 m S om, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504764</v>
+        <v>504825</v>
       </c>
       <c r="R5" t="n">
-        <v>6532946</v>
+        <v>6533191</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1080,7 +1092,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>ung, dikad sumpskog</t>
+          <t>kalhuggen våtmark</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1095,6 +1107,210 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118171591</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hagaberg, 450 m V om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>504880</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6533118</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>skogsbilvägkant</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125979595</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stora Janneberg, O om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>504764</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6532946</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>ung, dikad sumpskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 401-2023 artfynd.xlsx
+++ b/artfynd/A 401-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125979817</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
           <t>Fågelinventering Vätternvatten 2024</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129782196</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Artkartering projekt. Hallsberg-askersund</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121370634</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125979306</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,6 +1234,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118171591</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,8 +1341,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125979595</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>